--- a/artfynd/A 43837-2020 artfynd.xlsx
+++ b/artfynd/A 43837-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 43837-2020 artfynd.xlsx
+++ b/artfynd/A 43837-2020 artfynd.xlsx
@@ -1332,10 +1332,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121343125</v>
+        <v>121343128</v>
       </c>
       <c r="B8" t="n">
-        <v>57348</v>
+        <v>5189</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1344,20 +1344,20 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>105930</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1372,10 +1372,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>670886</v>
+        <v>670945</v>
       </c>
       <c r="R8" t="n">
-        <v>7116427</v>
+        <v>7116321</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1416,6 +1416,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1434,10 +1435,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121343128</v>
+        <v>121343125</v>
       </c>
       <c r="B9" t="n">
-        <v>5189</v>
+        <v>57348</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1446,20 +1447,20 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>105930</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1474,10 +1475,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>670945</v>
+        <v>670886</v>
       </c>
       <c r="R9" t="n">
-        <v>7116321</v>
+        <v>7116427</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1518,7 +1519,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 43837-2020 artfynd.xlsx
+++ b/artfynd/A 43837-2020 artfynd.xlsx
@@ -1026,10 +1026,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121343129</v>
+        <v>121340554</v>
       </c>
       <c r="B5" t="n">
-        <v>90652</v>
+        <v>78601</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1038,25 +1038,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1066,10 +1066,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>670945</v>
+        <v>670925</v>
       </c>
       <c r="R5" t="n">
-        <v>7116321</v>
+        <v>7116274</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1128,10 +1128,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121340554</v>
+        <v>121343130</v>
       </c>
       <c r="B6" t="n">
-        <v>78598</v>
+        <v>79711</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1140,25 +1140,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1168,10 +1168,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>670925</v>
+        <v>670928</v>
       </c>
       <c r="R6" t="n">
-        <v>7116274</v>
+        <v>7116291</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1233,7 +1233,7 @@
         <v>121343123</v>
       </c>
       <c r="B7" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1332,10 +1332,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121343128</v>
+        <v>121343129</v>
       </c>
       <c r="B8" t="n">
-        <v>5189</v>
+        <v>90662</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1348,21 +1348,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>105930</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1416,7 +1416,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1435,10 +1434,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121343125</v>
+        <v>121343128</v>
       </c>
       <c r="B9" t="n">
-        <v>57348</v>
+        <v>5189</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1447,20 +1446,20 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>105930</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1475,10 +1474,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>670886</v>
+        <v>670945</v>
       </c>
       <c r="R9" t="n">
-        <v>7116427</v>
+        <v>7116321</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1519,6 +1518,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1537,10 +1537,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121343130</v>
+        <v>121343126</v>
       </c>
       <c r="B10" t="n">
-        <v>79708</v>
+        <v>90715</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1549,25 +1549,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6462</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1577,10 +1577,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>670928</v>
+        <v>670885</v>
       </c>
       <c r="R10" t="n">
-        <v>7116291</v>
+        <v>7116380</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1639,10 +1639,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121343126</v>
+        <v>121343125</v>
       </c>
       <c r="B11" t="n">
-        <v>90705</v>
+        <v>57351</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1655,21 +1655,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1679,10 +1679,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>670885</v>
+        <v>670886</v>
       </c>
       <c r="R11" t="n">
-        <v>7116380</v>
+        <v>7116427</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 43837-2020 artfynd.xlsx
+++ b/artfynd/A 43837-2020 artfynd.xlsx
@@ -1026,10 +1026,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121340554</v>
+        <v>121343129</v>
       </c>
       <c r="B5" t="n">
-        <v>78601</v>
+        <v>90662</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1038,25 +1038,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1066,10 +1066,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>670925</v>
+        <v>670945</v>
       </c>
       <c r="R5" t="n">
-        <v>7116274</v>
+        <v>7116321</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1230,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121343123</v>
+        <v>121343125</v>
       </c>
       <c r="B7" t="n">
-        <v>78601</v>
+        <v>57351</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1246,21 +1246,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1270,10 +1270,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>670798</v>
+        <v>670886</v>
       </c>
       <c r="R7" t="n">
-        <v>7116451</v>
+        <v>7116427</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1332,10 +1332,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121343129</v>
+        <v>121343128</v>
       </c>
       <c r="B8" t="n">
-        <v>90662</v>
+        <v>5189</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1348,21 +1348,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>105930</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1416,6 +1416,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1434,10 +1435,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121343128</v>
+        <v>121343123</v>
       </c>
       <c r="B9" t="n">
-        <v>5189</v>
+        <v>78601</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1446,25 +1447,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>105930</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1474,10 +1475,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>670945</v>
+        <v>670798</v>
       </c>
       <c r="R9" t="n">
-        <v>7116321</v>
+        <v>7116451</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1518,7 +1519,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1639,10 +1639,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121343125</v>
+        <v>121340554</v>
       </c>
       <c r="B11" t="n">
-        <v>57351</v>
+        <v>78601</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1655,21 +1655,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1679,10 +1679,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>670886</v>
+        <v>670925</v>
       </c>
       <c r="R11" t="n">
-        <v>7116427</v>
+        <v>7116274</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 43837-2020 artfynd.xlsx
+++ b/artfynd/A 43837-2020 artfynd.xlsx
@@ -1026,10 +1026,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121343129</v>
+        <v>121343128</v>
       </c>
       <c r="B5" t="n">
-        <v>90662</v>
+        <v>5189</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1042,21 +1042,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5447</v>
+        <v>105930</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1110,6 +1110,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1128,10 +1129,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121343130</v>
+        <v>121343126</v>
       </c>
       <c r="B6" t="n">
-        <v>79711</v>
+        <v>90727</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1140,25 +1141,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6462</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1168,10 +1169,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>670928</v>
+        <v>670885</v>
       </c>
       <c r="R6" t="n">
-        <v>7116291</v>
+        <v>7116380</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1332,10 +1333,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121343128</v>
+        <v>121343123</v>
       </c>
       <c r="B8" t="n">
-        <v>5189</v>
+        <v>78604</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1344,25 +1345,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>105930</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1372,10 +1373,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>670945</v>
+        <v>670798</v>
       </c>
       <c r="R8" t="n">
-        <v>7116321</v>
+        <v>7116451</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1416,7 +1417,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1435,10 +1435,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121343123</v>
+        <v>121343129</v>
       </c>
       <c r="B9" t="n">
-        <v>78601</v>
+        <v>90674</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1447,25 +1447,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1475,10 +1475,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>670798</v>
+        <v>670945</v>
       </c>
       <c r="R9" t="n">
-        <v>7116451</v>
+        <v>7116321</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1537,10 +1537,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121343126</v>
+        <v>121340554</v>
       </c>
       <c r="B10" t="n">
-        <v>90715</v>
+        <v>78604</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1553,21 +1553,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1577,10 +1577,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>670885</v>
+        <v>670925</v>
       </c>
       <c r="R10" t="n">
-        <v>7116380</v>
+        <v>7116274</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1639,10 +1639,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121340554</v>
+        <v>121343130</v>
       </c>
       <c r="B11" t="n">
-        <v>78601</v>
+        <v>79714</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1651,25 +1651,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1679,10 +1679,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>670925</v>
+        <v>670928</v>
       </c>
       <c r="R11" t="n">
-        <v>7116274</v>
+        <v>7116291</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 43837-2020 artfynd.xlsx
+++ b/artfynd/A 43837-2020 artfynd.xlsx
@@ -1026,10 +1026,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121343128</v>
+        <v>121343123</v>
       </c>
       <c r="B5" t="n">
-        <v>5189</v>
+        <v>78604</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1038,25 +1038,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>105930</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1066,10 +1066,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>670945</v>
+        <v>670798</v>
       </c>
       <c r="R5" t="n">
-        <v>7116321</v>
+        <v>7116451</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1110,7 +1110,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1132,7 +1131,7 @@
         <v>121343126</v>
       </c>
       <c r="B6" t="n">
-        <v>90727</v>
+        <v>90728</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1333,7 +1332,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121343123</v>
+        <v>121340554</v>
       </c>
       <c r="B8" t="n">
         <v>78604</v>
@@ -1373,10 +1372,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>670798</v>
+        <v>670925</v>
       </c>
       <c r="R8" t="n">
-        <v>7116451</v>
+        <v>7116274</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1438,7 +1437,7 @@
         <v>121343129</v>
       </c>
       <c r="B9" t="n">
-        <v>90674</v>
+        <v>90675</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1537,10 +1536,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121340554</v>
+        <v>121343128</v>
       </c>
       <c r="B10" t="n">
-        <v>78604</v>
+        <v>5189</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1549,25 +1548,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>105930</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1577,10 +1576,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>670925</v>
+        <v>670945</v>
       </c>
       <c r="R10" t="n">
-        <v>7116274</v>
+        <v>7116321</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1621,6 +1620,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 43837-2020 artfynd.xlsx
+++ b/artfynd/A 43837-2020 artfynd.xlsx
@@ -1026,10 +1026,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121343123</v>
+        <v>121343130</v>
       </c>
       <c r="B5" t="n">
-        <v>78604</v>
+        <v>79717</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1038,25 +1038,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1066,10 +1066,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>670798</v>
+        <v>670928</v>
       </c>
       <c r="R5" t="n">
-        <v>7116451</v>
+        <v>7116291</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1128,10 +1128,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121343126</v>
+        <v>121343125</v>
       </c>
       <c r="B6" t="n">
-        <v>90728</v>
+        <v>57354</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1144,21 +1144,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1168,10 +1168,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>670885</v>
+        <v>670886</v>
       </c>
       <c r="R6" t="n">
-        <v>7116380</v>
+        <v>7116427</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1230,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121343125</v>
+        <v>121340554</v>
       </c>
       <c r="B7" t="n">
-        <v>57351</v>
+        <v>78607</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1246,21 +1246,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1270,10 +1270,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>670886</v>
+        <v>670925</v>
       </c>
       <c r="R7" t="n">
-        <v>7116427</v>
+        <v>7116274</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1332,10 +1332,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121340554</v>
+        <v>121343126</v>
       </c>
       <c r="B8" t="n">
-        <v>78604</v>
+        <v>90731</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1348,21 +1348,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1372,10 +1372,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>670925</v>
+        <v>670885</v>
       </c>
       <c r="R8" t="n">
-        <v>7116274</v>
+        <v>7116380</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1437,7 +1437,7 @@
         <v>121343129</v>
       </c>
       <c r="B9" t="n">
-        <v>90675</v>
+        <v>90678</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1536,10 +1536,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121343128</v>
+        <v>121343123</v>
       </c>
       <c r="B10" t="n">
-        <v>5189</v>
+        <v>78607</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1548,25 +1548,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>105930</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1576,10 +1576,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>670945</v>
+        <v>670798</v>
       </c>
       <c r="R10" t="n">
-        <v>7116321</v>
+        <v>7116451</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1620,7 +1620,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1639,10 +1638,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121343130</v>
+        <v>121343128</v>
       </c>
       <c r="B11" t="n">
-        <v>79714</v>
+        <v>5192</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1655,21 +1654,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6462</v>
+        <v>105930</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1679,10 +1678,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>670928</v>
+        <v>670945</v>
       </c>
       <c r="R11" t="n">
-        <v>7116291</v>
+        <v>7116321</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1723,6 +1722,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 43837-2020 artfynd.xlsx
+++ b/artfynd/A 43837-2020 artfynd.xlsx
@@ -1026,10 +1026,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121343130</v>
+        <v>121343125</v>
       </c>
       <c r="B5" t="n">
-        <v>79717</v>
+        <v>57354</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1038,25 +1038,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1066,10 +1066,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>670928</v>
+        <v>670886</v>
       </c>
       <c r="R5" t="n">
-        <v>7116291</v>
+        <v>7116427</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1128,10 +1128,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121343125</v>
+        <v>121343130</v>
       </c>
       <c r="B6" t="n">
-        <v>57354</v>
+        <v>79717</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1140,25 +1140,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1168,10 +1168,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>670886</v>
+        <v>670928</v>
       </c>
       <c r="R6" t="n">
-        <v>7116427</v>
+        <v>7116291</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1230,7 +1230,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121340554</v>
+        <v>121343123</v>
       </c>
       <c r="B7" t="n">
         <v>78607</v>
@@ -1270,10 +1270,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>670925</v>
+        <v>670798</v>
       </c>
       <c r="R7" t="n">
-        <v>7116274</v>
+        <v>7116451</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1332,10 +1332,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121343126</v>
+        <v>121343129</v>
       </c>
       <c r="B8" t="n">
-        <v>90731</v>
+        <v>90678</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1344,25 +1344,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1372,10 +1372,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>670885</v>
+        <v>670945</v>
       </c>
       <c r="R8" t="n">
-        <v>7116380</v>
+        <v>7116321</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1434,10 +1434,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121343129</v>
+        <v>121343128</v>
       </c>
       <c r="B9" t="n">
-        <v>90678</v>
+        <v>5192</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1450,21 +1450,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5447</v>
+        <v>105930</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1518,6 +1518,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1536,10 +1537,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121343123</v>
+        <v>121343126</v>
       </c>
       <c r="B10" t="n">
-        <v>78607</v>
+        <v>90731</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1552,21 +1553,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1576,10 +1577,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>670798</v>
+        <v>670885</v>
       </c>
       <c r="R10" t="n">
-        <v>7116451</v>
+        <v>7116380</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1638,10 +1639,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121343128</v>
+        <v>121340554</v>
       </c>
       <c r="B11" t="n">
-        <v>5192</v>
+        <v>78607</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1650,25 +1651,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>105930</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1678,10 +1679,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>670945</v>
+        <v>670925</v>
       </c>
       <c r="R11" t="n">
-        <v>7116321</v>
+        <v>7116274</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1722,7 +1723,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 43837-2020 artfynd.xlsx
+++ b/artfynd/A 43837-2020 artfynd.xlsx
@@ -1128,10 +1128,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121343130</v>
+        <v>121343123</v>
       </c>
       <c r="B6" t="n">
-        <v>79717</v>
+        <v>78607</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1140,25 +1140,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1168,10 +1168,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>670928</v>
+        <v>670798</v>
       </c>
       <c r="R6" t="n">
-        <v>7116291</v>
+        <v>7116451</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1230,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121343123</v>
+        <v>121343130</v>
       </c>
       <c r="B7" t="n">
-        <v>78607</v>
+        <v>79717</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1242,25 +1242,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1270,10 +1270,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>670798</v>
+        <v>670928</v>
       </c>
       <c r="R7" t="n">
-        <v>7116451</v>
+        <v>7116291</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 43837-2020 artfynd.xlsx
+++ b/artfynd/A 43837-2020 artfynd.xlsx
@@ -1029,7 +1029,7 @@
         <v>121343125</v>
       </c>
       <c r="B5" t="n">
-        <v>57354</v>
+        <v>57355</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1128,10 +1128,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121343123</v>
+        <v>121343128</v>
       </c>
       <c r="B6" t="n">
-        <v>78607</v>
+        <v>5192</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1140,25 +1140,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>105930</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1168,10 +1168,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>670798</v>
+        <v>670945</v>
       </c>
       <c r="R6" t="n">
-        <v>7116451</v>
+        <v>7116321</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1212,6 +1212,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1230,10 +1231,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121343130</v>
+        <v>121340554</v>
       </c>
       <c r="B7" t="n">
-        <v>79717</v>
+        <v>78608</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1242,25 +1243,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1270,10 +1271,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>670928</v>
+        <v>670925</v>
       </c>
       <c r="R7" t="n">
-        <v>7116291</v>
+        <v>7116274</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1332,10 +1333,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121343129</v>
+        <v>121343126</v>
       </c>
       <c r="B8" t="n">
-        <v>90678</v>
+        <v>90737</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1344,25 +1345,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1372,10 +1373,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>670945</v>
+        <v>670885</v>
       </c>
       <c r="R8" t="n">
-        <v>7116321</v>
+        <v>7116380</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1434,10 +1435,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121343128</v>
+        <v>121343129</v>
       </c>
       <c r="B9" t="n">
-        <v>5192</v>
+        <v>90684</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1450,21 +1451,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>105930</v>
+        <v>5447</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1518,7 +1519,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1537,10 +1537,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121343126</v>
+        <v>121343123</v>
       </c>
       <c r="B10" t="n">
-        <v>90731</v>
+        <v>78608</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1553,21 +1553,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1577,10 +1577,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>670885</v>
+        <v>670798</v>
       </c>
       <c r="R10" t="n">
-        <v>7116380</v>
+        <v>7116451</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1639,10 +1639,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121340554</v>
+        <v>121343130</v>
       </c>
       <c r="B11" t="n">
-        <v>78607</v>
+        <v>79718</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1651,25 +1651,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1679,10 +1679,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>670925</v>
+        <v>670928</v>
       </c>
       <c r="R11" t="n">
-        <v>7116274</v>
+        <v>7116291</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 43837-2020 artfynd.xlsx
+++ b/artfynd/A 43837-2020 artfynd.xlsx
@@ -1231,10 +1231,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121340554</v>
+        <v>121343126</v>
       </c>
       <c r="B7" t="n">
-        <v>78608</v>
+        <v>90737</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1247,21 +1247,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1271,10 +1271,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>670925</v>
+        <v>670885</v>
       </c>
       <c r="R7" t="n">
-        <v>7116274</v>
+        <v>7116380</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1333,10 +1333,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121343126</v>
+        <v>121340554</v>
       </c>
       <c r="B8" t="n">
-        <v>90737</v>
+        <v>78608</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1349,21 +1349,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1373,10 +1373,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>670885</v>
+        <v>670925</v>
       </c>
       <c r="R8" t="n">
-        <v>7116380</v>
+        <v>7116274</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>

--- a/artfynd/A 43837-2020 artfynd.xlsx
+++ b/artfynd/A 43837-2020 artfynd.xlsx
@@ -1026,10 +1026,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121343125</v>
+        <v>121343130</v>
       </c>
       <c r="B5" t="n">
-        <v>57355</v>
+        <v>79719</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1038,25 +1038,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1066,10 +1066,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>670886</v>
+        <v>670928</v>
       </c>
       <c r="R5" t="n">
-        <v>7116427</v>
+        <v>7116291</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1128,10 +1128,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121343128</v>
+        <v>121343129</v>
       </c>
       <c r="B6" t="n">
-        <v>5192</v>
+        <v>90685</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1144,21 +1144,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>105930</v>
+        <v>5447</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1212,7 +1212,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1234,7 +1233,7 @@
         <v>121343126</v>
       </c>
       <c r="B7" t="n">
-        <v>90737</v>
+        <v>90738</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1333,10 +1332,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121340554</v>
+        <v>121343128</v>
       </c>
       <c r="B8" t="n">
-        <v>78608</v>
+        <v>5192</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1345,25 +1344,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>105930</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1373,10 +1372,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>670925</v>
+        <v>670945</v>
       </c>
       <c r="R8" t="n">
-        <v>7116274</v>
+        <v>7116321</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1417,6 +1416,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1435,10 +1435,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121343129</v>
+        <v>121343125</v>
       </c>
       <c r="B9" t="n">
-        <v>90684</v>
+        <v>57356</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1447,25 +1447,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1475,10 +1475,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>670945</v>
+        <v>670886</v>
       </c>
       <c r="R9" t="n">
-        <v>7116321</v>
+        <v>7116427</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1540,7 +1540,7 @@
         <v>121343123</v>
       </c>
       <c r="B10" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121343130</v>
+        <v>121340554</v>
       </c>
       <c r="B11" t="n">
-        <v>79718</v>
+        <v>78609</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1651,25 +1651,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1679,10 +1679,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>670928</v>
+        <v>670925</v>
       </c>
       <c r="R11" t="n">
-        <v>7116291</v>
+        <v>7116274</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 43837-2020 artfynd.xlsx
+++ b/artfynd/A 43837-2020 artfynd.xlsx
@@ -1026,10 +1026,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121343130</v>
+        <v>121343125</v>
       </c>
       <c r="B5" t="n">
-        <v>79719</v>
+        <v>57356</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1038,25 +1038,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1066,10 +1066,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>670928</v>
+        <v>670886</v>
       </c>
       <c r="R5" t="n">
-        <v>7116291</v>
+        <v>7116427</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1128,10 +1128,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121343129</v>
+        <v>121343130</v>
       </c>
       <c r="B6" t="n">
-        <v>90685</v>
+        <v>79719</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1144,21 +1144,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5447</v>
+        <v>6462</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1168,10 +1168,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>670945</v>
+        <v>670928</v>
       </c>
       <c r="R6" t="n">
-        <v>7116321</v>
+        <v>7116291</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1230,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121343126</v>
+        <v>121340554</v>
       </c>
       <c r="B7" t="n">
-        <v>90738</v>
+        <v>78609</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1246,21 +1246,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1270,10 +1270,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>670885</v>
+        <v>670925</v>
       </c>
       <c r="R7" t="n">
-        <v>7116380</v>
+        <v>7116274</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1332,10 +1332,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121343128</v>
+        <v>121343126</v>
       </c>
       <c r="B8" t="n">
-        <v>5192</v>
+        <v>90738</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1344,25 +1344,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>105930</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1372,10 +1372,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>670945</v>
+        <v>670885</v>
       </c>
       <c r="R8" t="n">
-        <v>7116321</v>
+        <v>7116380</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1416,7 +1416,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1435,10 +1434,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121343125</v>
+        <v>121343129</v>
       </c>
       <c r="B9" t="n">
-        <v>57356</v>
+        <v>90685</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1447,25 +1446,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1475,10 +1474,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>670886</v>
+        <v>670945</v>
       </c>
       <c r="R9" t="n">
-        <v>7116427</v>
+        <v>7116321</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1537,10 +1536,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121343123</v>
+        <v>121343128</v>
       </c>
       <c r="B10" t="n">
-        <v>78609</v>
+        <v>5192</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1549,25 +1548,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>105930</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1577,10 +1576,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>670798</v>
+        <v>670945</v>
       </c>
       <c r="R10" t="n">
-        <v>7116451</v>
+        <v>7116321</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1621,6 +1620,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1639,7 +1639,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121340554</v>
+        <v>121343123</v>
       </c>
       <c r="B11" t="n">
         <v>78609</v>
@@ -1679,10 +1679,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>670925</v>
+        <v>670798</v>
       </c>
       <c r="R11" t="n">
-        <v>7116274</v>
+        <v>7116451</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 43837-2020 artfynd.xlsx
+++ b/artfynd/A 43837-2020 artfynd.xlsx
@@ -1026,10 +1026,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121343125</v>
+        <v>121343126</v>
       </c>
       <c r="B5" t="n">
-        <v>57356</v>
+        <v>90738</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1042,21 +1042,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1066,10 +1066,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>670886</v>
+        <v>670885</v>
       </c>
       <c r="R5" t="n">
-        <v>7116427</v>
+        <v>7116380</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1128,10 +1128,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121343130</v>
+        <v>121343125</v>
       </c>
       <c r="B6" t="n">
-        <v>79719</v>
+        <v>57356</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1140,25 +1140,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1168,10 +1168,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>670928</v>
+        <v>670886</v>
       </c>
       <c r="R6" t="n">
-        <v>7116291</v>
+        <v>7116427</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1230,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121340554</v>
+        <v>121343128</v>
       </c>
       <c r="B7" t="n">
-        <v>78609</v>
+        <v>5192</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1242,25 +1242,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>105930</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1270,10 +1270,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>670925</v>
+        <v>670945</v>
       </c>
       <c r="R7" t="n">
-        <v>7116274</v>
+        <v>7116321</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1314,6 +1314,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1332,10 +1333,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121343126</v>
+        <v>121340554</v>
       </c>
       <c r="B8" t="n">
-        <v>90738</v>
+        <v>78609</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1348,21 +1349,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1372,10 +1373,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>670885</v>
+        <v>670925</v>
       </c>
       <c r="R8" t="n">
-        <v>7116380</v>
+        <v>7116274</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1536,10 +1537,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121343128</v>
+        <v>121343130</v>
       </c>
       <c r="B10" t="n">
-        <v>5192</v>
+        <v>79719</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1552,21 +1553,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>105930</v>
+        <v>6462</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1576,10 +1577,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>670945</v>
+        <v>670928</v>
       </c>
       <c r="R10" t="n">
-        <v>7116321</v>
+        <v>7116291</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1620,7 +1621,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 43837-2020 artfynd.xlsx
+++ b/artfynd/A 43837-2020 artfynd.xlsx
@@ -1026,10 +1026,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121343126</v>
+        <v>121343125</v>
       </c>
       <c r="B5" t="n">
-        <v>90738</v>
+        <v>57356</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1042,21 +1042,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1066,10 +1066,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>670885</v>
+        <v>670886</v>
       </c>
       <c r="R5" t="n">
-        <v>7116380</v>
+        <v>7116427</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1128,10 +1128,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121343125</v>
+        <v>121343128</v>
       </c>
       <c r="B6" t="n">
-        <v>57356</v>
+        <v>5192</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1140,20 +1140,20 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>105930</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1168,10 +1168,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>670886</v>
+        <v>670945</v>
       </c>
       <c r="R6" t="n">
-        <v>7116427</v>
+        <v>7116321</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1212,6 +1212,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1230,10 +1231,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121343128</v>
+        <v>121343126</v>
       </c>
       <c r="B7" t="n">
-        <v>5192</v>
+        <v>90738</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1242,25 +1243,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>105930</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1270,10 +1271,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>670945</v>
+        <v>670885</v>
       </c>
       <c r="R7" t="n">
-        <v>7116321</v>
+        <v>7116380</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1314,7 +1315,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1435,10 +1435,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121343129</v>
+        <v>121343123</v>
       </c>
       <c r="B9" t="n">
-        <v>90685</v>
+        <v>78609</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1447,25 +1447,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1475,10 +1475,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>670945</v>
+        <v>670798</v>
       </c>
       <c r="R9" t="n">
-        <v>7116321</v>
+        <v>7116451</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1639,10 +1639,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121343123</v>
+        <v>121343129</v>
       </c>
       <c r="B11" t="n">
-        <v>78609</v>
+        <v>90685</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1651,25 +1651,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1679,10 +1679,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>670798</v>
+        <v>670945</v>
       </c>
       <c r="R11" t="n">
-        <v>7116451</v>
+        <v>7116321</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 43837-2020 artfynd.xlsx
+++ b/artfynd/A 43837-2020 artfynd.xlsx
@@ -1026,10 +1026,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121343125</v>
+        <v>121343126</v>
       </c>
       <c r="B5" t="n">
-        <v>57356</v>
+        <v>90746</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1042,21 +1042,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1066,10 +1066,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>670886</v>
+        <v>670885</v>
       </c>
       <c r="R5" t="n">
-        <v>7116427</v>
+        <v>7116380</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1128,10 +1128,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121343128</v>
+        <v>121343130</v>
       </c>
       <c r="B6" t="n">
-        <v>5192</v>
+        <v>79726</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1144,21 +1144,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>105930</v>
+        <v>6462</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1168,10 +1168,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>670945</v>
+        <v>670928</v>
       </c>
       <c r="R6" t="n">
-        <v>7116321</v>
+        <v>7116291</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1212,7 +1212,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1231,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121343126</v>
+        <v>121343125</v>
       </c>
       <c r="B7" t="n">
-        <v>90738</v>
+        <v>57357</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1247,21 +1246,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1271,10 +1270,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>670885</v>
+        <v>670886</v>
       </c>
       <c r="R7" t="n">
-        <v>7116380</v>
+        <v>7116427</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1333,10 +1332,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121340554</v>
+        <v>121343128</v>
       </c>
       <c r="B8" t="n">
-        <v>78609</v>
+        <v>5193</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1345,25 +1344,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>105930</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1373,10 +1372,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>670925</v>
+        <v>670945</v>
       </c>
       <c r="R8" t="n">
-        <v>7116274</v>
+        <v>7116321</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1417,6 +1416,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1435,10 +1435,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121343123</v>
+        <v>121340554</v>
       </c>
       <c r="B9" t="n">
-        <v>78609</v>
+        <v>78616</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1475,10 +1475,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>670798</v>
+        <v>670925</v>
       </c>
       <c r="R9" t="n">
-        <v>7116451</v>
+        <v>7116274</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1537,10 +1537,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121343130</v>
+        <v>121343123</v>
       </c>
       <c r="B10" t="n">
-        <v>79719</v>
+        <v>78616</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1549,25 +1549,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1577,10 +1577,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>670928</v>
+        <v>670798</v>
       </c>
       <c r="R10" t="n">
-        <v>7116291</v>
+        <v>7116451</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1642,7 +1642,7 @@
         <v>121343129</v>
       </c>
       <c r="B11" t="n">
-        <v>90685</v>
+        <v>90693</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
